--- a/shucle_report/해안면/20260413_20260419/report_해안면_20260413_20260419.xlsx
+++ b/shucle_report/해안면/20260413_20260419/report_해안면_20260413_20260419.xlsx
@@ -505,7 +505,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.04.13 ~ 04.19 | 비교기간: 2026.04.06 ~ 04.12 | 생성: 2026-04-20 11:27 | 차트: 102개</t>
+          <t>분석기간: 2026.04.13 ~ 04.19 | 비교기간: 2026.04.06 ~ 04.12 | 생성: 2026-04-20 12:35 | 차트: 109개</t>
         </is>
       </c>
     </row>
@@ -578,22 +578,22 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8.0건</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2.2건</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>+37.9%</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>⚠ 증가</t>
         </is>
       </c>
     </row>
@@ -615,22 +615,22 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7.6건</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2.2건</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>+40.7%</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>⚠ 증가</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9.0명</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2.4명</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>+36.4%</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>⚠ 증가</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1117,7 +1117,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>▲ 대당 탑승객 수(일평균) (+36.4%)</t>
+          <t>▲ 실시간 호출 건수(일평균) (+37.9%)</t>
         </is>
       </c>
     </row>
@@ -1161,192 +1161,192 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>대당 탑승객 수(일평균)</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>대당 탑승객 수(평일)</t>
+          <t>이동완료 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>+2.4</t>
+          <t>+2.2</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>+36.4%</t>
+          <t>+40.7%</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>평일 9.0명 (36% 증가)</t>
+          <t>동반 증가 (41%)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>대당 탑승객 수(일평균)</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>대당 탑승객 수(주말)</t>
+          <t>평균 대기시간</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>3.8→2.9분 감소</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>대당 탑승객 수(일평균)</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>동승 인원 분포(일평균)</t>
+          <t>전화 호출 비율</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+18.4%p</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+76.1%</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>분석기간 데이터 없음</t>
+          <t>전화 24→42%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>대당 탑승객 수(일평균)</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>실시간 호출 건수(일평균)</t>
+          <t>앱 호출 비율</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-19.2%p</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-37.2%</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>분석기간 데이터 없음</t>
+          <t>앱 52→32%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>대당 탑승객 수(일평균)</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>운행차량 대수</t>
+          <t>현장 호출 비율</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.9%p</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+3.6%</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>1대 유지, 증차 여지 없음</t>
+          <t>현장 비중 유지</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>▲ 대당 운행거리(일평균) (+18.9%)</t>
+          <t>▲ 이동완료 호출 건수(일평균) (+40.7%)</t>
         </is>
       </c>
     </row>
@@ -1390,118 +1390,118 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>대당 운행거리(일평균)</t>
+          <t>이동완료 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>일간 평균 대당 운행거리</t>
+          <t>미탑승 건수(일평균)</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>+7.6</t>
+          <t>+0.2</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>+18.9%</t>
+          <t>+inf%</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>동반 증가 (19%)</t>
+          <t>미발생→0건 신규 발생</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>대당 운행거리(일평균)</t>
+          <t>이동완료 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>실시간 호출 건수(일평균)</t>
+          <t>호출취소 건수(일평균)</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+0.2</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+inf%</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>분석기간 데이터 없음</t>
+          <t>미발생→0건 신규 발생</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>대당 운행거리(일평균)</t>
+          <t>이동완료 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>운행차량 대수</t>
+          <t>배차실패 건수(일평균)</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>1대 유지, 증차 여지 없음</t>
+          <t>배차실패 건수 해소</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>▲ DAU (일간 활성 회원) (+42.9%)</t>
+          <t>▲ 총 탑승객 수(일평균) (+36.4%)</t>
         </is>
       </c>
     </row>
@@ -1545,313 +1545,892 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>DAU (일간 활성 회원)</t>
+          <t>총 탑승객 수(일평균)</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>WAU (주간 활성 회원)</t>
+          <t>동승 인원 분포(일평균)</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>+1.4</t>
+          <t>+2.4</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>+87.5%</t>
+          <t>+36.4%</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>1.6→3.0명 증가</t>
+          <t>동반 증가 (36%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>DAU (일간 활성 회원)</t>
+          <t>총 탑승객 수(일평균)</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>신규 지역 회원(일평균)</t>
+          <t>고령자(60+) 호출 비율</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>+0.2</t>
+          <t>-18.5%p</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>+50.0%</t>
+          <t>-21.3%</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>신규 0.6명/일 (50% 증가)</t>
+          <t>고령자(60+) 비중 69%로 주도적</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>DAU (일간 활성 회원)</t>
+          <t>총 탑승객 수(일평균)</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>활성 회원 평균연령</t>
+          <t>성인(20~50대) 호출 비율</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>+10.0</t>
+          <t>+10.6%p</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>+16.7%</t>
+          <t>+81.9%</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>평균 70세 (17% 증가)</t>
+          <t>성인(20~50대) 13→24%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>DAU (일간 활성 회원)</t>
+          <t>총 탑승객 수(일평균)</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>가호출 성공률</t>
+          <t>어린이/청소년 호출 비율</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>-12.3%p</t>
+          <t>+7.9%p</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>+inf%</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>소폭 역방향 감소</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>DAU (일간 활성 회원)</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>평균 대기시간</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>2.9</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>-0.9</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>-24.0%</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>3.8→2.9분 감소</t>
+          <t>신규 발생</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>▲ 대당 탑승객 수(일평균) (+36.4%)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>▲ 신규 지역 회원(일평균) (+50.0%)</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>세부지표</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>비교기간</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>분석기간</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>변동값</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>변동률</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>포인트</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>세부지표</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>비교기간</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>분석기간</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>변동값</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>변동률</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>포인트</t>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>대당 탑승객 수(일평균)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>대당 탑승객 수(평일)</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>+2.4</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>+36.4%</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>평일 9.0명 (36% 증가)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>신규 지역 회원(일평균)</t>
+          <t>대당 탑승객 수(일평균)</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>누적 지역 회원(일평균)</t>
+          <t>대당 탑승객 수(주말)</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>+16.4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>+215.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>누적 24명 (216% 증가)</t>
+          <t>데이터 없음</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
+          <t>대당 탑승객 수(일평균)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>동승 인원 분포(일평균)</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>+2.4</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>+36.4%</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>동반 증가 (36%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>대당 탑승객 수(일평균)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>실시간 호출 건수(일평균)</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>+2.2</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>+37.9%</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>동반 증가 (38%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>대당 탑승객 수(일평균)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>운행차량 대수</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>+0.0</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>1대 유지, 증차 여지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>▲ 대당 운행거리(일평균) (+18.9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>세부지표</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>비교기간</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>분석기간</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>변동값</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>변동률</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>대당 운행거리(일평균)</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>일간 평균 대당 운행거리</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>40.2</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>47.8</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>+7.6</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>+18.9%</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>동반 증가 (19%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>대당 운행거리(일평균)</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>실시간 호출 건수(일평균)</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>+2.2</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>+37.9%</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>38% 증가, 핵심 요인</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>대당 운행거리(일평균)</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>운행차량 대수</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>+0.0</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>1대 유지, 증차 여지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>▲ DAU (일간 활성 회원) (+42.9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>세부지표</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>비교기간</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>분석기간</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>변동값</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>변동률</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>DAU (일간 활성 회원)</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>WAU (주간 활성 회원)</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>+1.4</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>+87.5%</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>1.6→3.0명 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>DAU (일간 활성 회원)</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
           <t>신규 지역 회원(일평균)</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>+0.2</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>+50.0%</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>신규 0.6명/일 (50% 증가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>DAU (일간 활성 회원)</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>활성 회원 평균연령</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>+10.0</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>+16.7%</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>평균 70세 (17% 증가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>DAU (일간 활성 회원)</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>가호출 성공률</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>97.5%</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>85.2%</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>-12.3%p</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>-12.6%</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>소폭 역방향 감소</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>DAU (일간 활성 회원)</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>평균 대기시간</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>-0.9</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>-24.0%</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>3.8→2.9분 감소</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>▲ 신규 지역 회원(일평균) (+50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>세부지표</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>비교기간</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>분석기간</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>변동값</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>변동률</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>신규 지역 회원(일평균)</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>누적 지역 회원(일평균)</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>+16.4</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>+215.8%</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>누적 24명 (216% 증가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>신규 지역 회원(일평균)</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>가호출 순 회원(일평균)</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>+1.2</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>+42.9%</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="G49" s="6" t="inlineStr">
         <is>
           <t>2.8→4.0명 증가</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="8">
+    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A38:G38"/>
     <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A46:G46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1879,28 +2458,28 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>• 대기시간 개선: 3.8분 → 2.9분 (-24%) — 특히 04/13 상위10% 대기시간 9.1분으로 극단치 발생</t>
+          <t>• 수요 증가: 호출(+38%), 이동완료(+41%), 탑승객(+36%) 모두 상승 — 분석기간 운행 5일(04/13,04/14,04/15,04/16,04/17), 비교기간 5일</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>• 성장 지표 긍정적: DAU +43%, 신규회원 0→1명(+50%), 누적 41명 — 이용자 기반 확대 추세</t>
+          <t>• 이동완료율 93.1% → 95.0% (+1.9%p): 호출 8건 중 8건 완료 (호출취소 1건, 배차실패 0건)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>• 가호출 성공률 안정: 97.5% → 100.0% (+2.6%)</t>
+          <t>• 대기시간 개선: 3.8분 → 2.9분 (-24%) — 특히 04/13 상위10% 대기시간 9.1분으로 극단치 발생</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>• 공급 현황: 운행차량 1.0대, 대당 운행시간 7.1시간</t>
+          <t>• 성장 지표 긍정적: DAU +43%, 신규회원 0→1명(+50%), 누적 41명 — 이용자 기반 확대 추세</t>
         </is>
       </c>
     </row>
@@ -2184,22 +2763,22 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2.2</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+37.9%</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>분석기간 데이터 없음</t>
+          <t>역방향 증가 (38%)</t>
         </is>
       </c>
     </row>
@@ -2339,22 +2918,22 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2.4</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+36.4%</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>분석기간 데이터 없음</t>
+          <t>36% 증가, 핵심 요인</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2989,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>피크 시간대 이동시간</t>
+          <t>피크 시간대(16~18시) 이동시간</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -2420,22 +2999,22 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>분석기간 데이터 없음</t>
+          <t>5.4→4.2분 감소</t>
         </is>
       </c>
     </row>
@@ -2447,7 +3026,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>비피크 시간대 이동시간</t>
+          <t>비피크 시간대(8~10시) 이동시간</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -2457,22 +3036,22 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+46.8%</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>분석기간 데이터 없음</t>
+          <t>4.3→6.3분 증가</t>
         </is>
       </c>
     </row>
@@ -2649,22 +3228,22 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>분석기간 데이터 없음</t>
+          <t>배차실패 건수 해소</t>
         </is>
       </c>
     </row>
